--- a/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.36926347924742</v>
+        <v>45.05906166705924</v>
       </c>
       <c r="M2" t="n">
-        <v>100.0297325595653</v>
+        <v>100.8718419923032</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98363545321975</v>
+        <v>88.04584880523784</v>
       </c>
       <c r="C3" t="n">
-        <v>45.86334899086266</v>
+        <v>45.93959165392831</v>
       </c>
       <c r="D3" t="n">
-        <v>2.22866810598734</v>
+        <v>2.228769893903327</v>
       </c>
       <c r="E3" t="n">
-        <v>5.666818713987221</v>
+        <v>5.713579121241905</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428893686624467</v>
+        <v>0.7429232979677758</v>
       </c>
       <c r="G3" t="n">
-        <v>33.95086678207227</v>
+        <v>33.97671886042365</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17291095847255</v>
+        <v>34.17447170651768</v>
       </c>
       <c r="I3" t="n">
-        <v>6.578422969897619</v>
+        <v>6.566115312884911</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643058554140292</v>
+        <v>4.643270612298599</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01636454678027</v>
+        <v>11.95415119476215</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8841481893778</v>
+        <v>48.87057143675116</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7638617270207</v>
+        <v>106.7643142854416</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.14710366048054</v>
+        <v>87.13159293506162</v>
       </c>
       <c r="C4" t="n">
-        <v>42.66638103490029</v>
+        <v>42.65969576348334</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18870517136003</v>
+        <v>2.184733660509007</v>
       </c>
       <c r="E4" t="n">
-        <v>6.480794947915474</v>
+        <v>6.514563184319801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444503657135549</v>
+        <v>0.7444817175186899</v>
       </c>
       <c r="G4" t="n">
-        <v>33.34208332700892</v>
+        <v>33.3054038333302</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24471682282353</v>
+        <v>34.24615900585972</v>
       </c>
       <c r="I4" t="n">
-        <v>5.493538239949299</v>
+        <v>5.483240799032392</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652814785709718</v>
+        <v>4.653010734491811</v>
       </c>
       <c r="K4" t="n">
-        <v>12.85289633951949</v>
+        <v>12.86840706493838</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29798865419419</v>
+        <v>44.28950507955371</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81726602861396</v>
+        <v>99.81760790797543</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.12868292609058</v>
+        <v>86.01325471961869</v>
       </c>
       <c r="C5" t="n">
-        <v>42.50060449982321</v>
+        <v>42.39240540232259</v>
       </c>
       <c r="D5" t="n">
-        <v>2.139438379409465</v>
+        <v>2.130339452546928</v>
       </c>
       <c r="E5" t="n">
-        <v>7.099260750289099</v>
+        <v>7.115279625639134</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457716848819536</v>
+        <v>0.7458023841460784</v>
       </c>
       <c r="G5" t="n">
-        <v>32.59156767786398</v>
+        <v>32.47618556516423</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30549750456986</v>
+        <v>34.30690967071959</v>
       </c>
       <c r="I5" t="n">
-        <v>4.586073898564001</v>
+        <v>4.577473120489739</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66107303051221</v>
+        <v>4.66126490091299</v>
       </c>
       <c r="K5" t="n">
-        <v>13.87131707390944</v>
+        <v>13.98674528038131</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47548014182433</v>
+        <v>43.46853707287853</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84740171555697</v>
+        <v>99.84768775558244</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.80189264113758</v>
+        <v>84.74487908988827</v>
       </c>
       <c r="C6" t="n">
-        <v>41.88620291562539</v>
+        <v>41.83499155338953</v>
       </c>
       <c r="D6" t="n">
-        <v>2.074695403360638</v>
+        <v>2.068679326351935</v>
       </c>
       <c r="E6" t="n">
-        <v>7.522338264039085</v>
+        <v>7.546051860999356</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468936821216048</v>
+        <v>0.7469230747065323</v>
       </c>
       <c r="G6" t="n">
-        <v>31.60529244513487</v>
+        <v>31.53620123642922</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35710937759382</v>
+        <v>34.35846143650047</v>
       </c>
       <c r="I6" t="n">
-        <v>3.827477955627526</v>
+        <v>3.820292937984926</v>
       </c>
       <c r="J6" t="n">
-        <v>4.66808551326003</v>
+        <v>4.668269216915826</v>
       </c>
       <c r="K6" t="n">
-        <v>15.19810735886243</v>
+        <v>15.25512091011173</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78829878388541</v>
+        <v>42.78273550537403</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87260905837323</v>
+        <v>99.87284796887529</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.35709414995355</v>
+        <v>83.2424886191164</v>
       </c>
       <c r="C7" t="n">
-        <v>41.03601546397603</v>
+        <v>40.92606126910194</v>
       </c>
       <c r="D7" t="n">
-        <v>2.004500914338146</v>
+        <v>1.995697512399048</v>
       </c>
       <c r="E7" t="n">
-        <v>7.800103264308166</v>
+        <v>7.81110502183174</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478475334663329</v>
+        <v>0.7478764831342606</v>
       </c>
       <c r="G7" t="n">
-        <v>30.53597048587325</v>
+        <v>30.423622238757</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40098653945132</v>
+        <v>34.40231822417597</v>
       </c>
       <c r="I7" t="n">
-        <v>3.193638328351769</v>
+        <v>3.187641119229249</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674047084164581</v>
+        <v>4.674228019589128</v>
       </c>
       <c r="K7" t="n">
-        <v>16.64290585004643</v>
+        <v>16.75751138088362</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21475985387679</v>
+        <v>42.21030810173706</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89368116789926</v>
+        <v>99.89388075172261</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.25852639269792</v>
+        <v>88.11653566089227</v>
       </c>
       <c r="C8" t="n">
-        <v>43.3544562573869</v>
+        <v>43.19490628831993</v>
       </c>
       <c r="D8" t="n">
-        <v>2.008780590554953</v>
+        <v>1.999977047526031</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644729645490219</v>
+        <v>9.623686178935808</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494442128591333</v>
+        <v>0.7494802149925873</v>
       </c>
       <c r="G8" t="n">
-        <v>31.04406501661591</v>
+        <v>30.91438916804852</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47443379152013</v>
+        <v>34.476089889659</v>
       </c>
       <c r="I8" t="n">
-        <v>5.653046805287969</v>
+        <v>5.668661818026659</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684026330369583</v>
+        <v>4.684251343703671</v>
       </c>
       <c r="K8" t="n">
-        <v>11.74147360730209</v>
+        <v>11.88346433910772</v>
       </c>
       <c r="L8" t="n">
-        <v>44.71603669944987</v>
+        <v>44.73307830390117</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81196656413886</v>
+        <v>99.81144893132881</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.49227321185595</v>
+        <v>86.16395643776313</v>
       </c>
       <c r="C9" t="n">
-        <v>42.46591167430158</v>
+        <v>42.12226752776638</v>
       </c>
       <c r="D9" t="n">
-        <v>1.929186674121572</v>
+        <v>1.911667749480626</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0491499430124</v>
+        <v>9.98750639245179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508073240066351</v>
+        <v>0.750852382016712</v>
       </c>
       <c r="G9" t="n">
-        <v>29.81400598065004</v>
+        <v>29.54935949917811</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53713690430521</v>
+        <v>34.53920957276874</v>
       </c>
       <c r="I9" t="n">
-        <v>4.719440610718603</v>
+        <v>4.732533454262698</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692545775041469</v>
+        <v>4.69282738760445</v>
       </c>
       <c r="K9" t="n">
-        <v>13.50772678814405</v>
+        <v>13.83604356223687</v>
       </c>
       <c r="L9" t="n">
-        <v>43.86933245962969</v>
+        <v>43.88422608171822</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84297092207532</v>
+        <v>99.84253717172147</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.50520086870128</v>
+        <v>84.11511048306014</v>
       </c>
       <c r="C10" t="n">
-        <v>41.21155544123579</v>
+        <v>40.8078363815163</v>
       </c>
       <c r="D10" t="n">
-        <v>1.840315875529548</v>
+        <v>1.82001635180852</v>
       </c>
       <c r="E10" t="n">
-        <v>10.24271749634112</v>
+        <v>10.16699892621762</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519738847144176</v>
+        <v>0.7520276881511894</v>
       </c>
       <c r="G10" t="n">
-        <v>28.44058030014445</v>
+        <v>28.13266975319533</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59079869686321</v>
+        <v>34.59327365495469</v>
       </c>
       <c r="I10" t="n">
-        <v>3.938977835643411</v>
+        <v>3.949951057787864</v>
       </c>
       <c r="J10" t="n">
-        <v>4.69983677946511</v>
+        <v>4.700173050944933</v>
       </c>
       <c r="K10" t="n">
-        <v>15.49479913129872</v>
+        <v>15.88488951693985</v>
       </c>
       <c r="L10" t="n">
-        <v>43.16254985494552</v>
+        <v>43.17581483892544</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86890442748003</v>
+        <v>99.86854073738159</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.40025205930019</v>
+        <v>81.92143778798432</v>
       </c>
       <c r="C11" t="n">
-        <v>39.71771900227893</v>
+        <v>39.22664433787847</v>
       </c>
       <c r="D11" t="n">
-        <v>1.747042781132975</v>
+        <v>1.722808540226829</v>
       </c>
       <c r="E11" t="n">
-        <v>10.27139148185044</v>
+        <v>10.17331545772734</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529737288878906</v>
+        <v>0.7530362616151334</v>
       </c>
       <c r="G11" t="n">
-        <v>26.99912072991423</v>
+        <v>26.63009245055676</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63679152884296</v>
+        <v>34.63966803429611</v>
       </c>
       <c r="I11" t="n">
-        <v>3.286846003122358</v>
+        <v>3.296040408467562</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706085805549315</v>
+        <v>4.706476635094583</v>
       </c>
       <c r="K11" t="n">
-        <v>17.59974794069981</v>
+        <v>18.07856221201568</v>
       </c>
       <c r="L11" t="n">
-        <v>42.57311700603116</v>
+        <v>42.58507258738951</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89058394900991</v>
+        <v>99.89027913728366</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.1599414412557</v>
+        <v>79.6478950104985</v>
       </c>
       <c r="C12" t="n">
-        <v>37.98672449306363</v>
+        <v>37.46349332270519</v>
       </c>
       <c r="D12" t="n">
-        <v>1.648608796828372</v>
+        <v>1.623006330766918</v>
       </c>
       <c r="E12" t="n">
-        <v>10.14969533475762</v>
+        <v>10.04228604629545</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538323354972395</v>
+        <v>0.7539028864495828</v>
       </c>
       <c r="G12" t="n">
-        <v>25.4779038170445</v>
+        <v>25.08741257485952</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67628743287301</v>
+        <v>34.67953277668079</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74216162739723</v>
+        <v>2.749861355136345</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711452096857746</v>
+        <v>4.711893040309892</v>
       </c>
       <c r="K12" t="n">
-        <v>19.84005855874427</v>
+        <v>20.35210498950149</v>
       </c>
       <c r="L12" t="n">
-        <v>42.08191567032758</v>
+        <v>42.09284500978033</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90869872213548</v>
+        <v>99.90844332198702</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.85841696501623</v>
+        <v>77.21079143892497</v>
       </c>
       <c r="C13" t="n">
-        <v>36.10937158947118</v>
+        <v>35.45142945501132</v>
       </c>
       <c r="D13" t="n">
-        <v>1.548334428144022</v>
+        <v>1.516884042095624</v>
       </c>
       <c r="E13" t="n">
-        <v>9.913582787040278</v>
+        <v>9.767962079094138</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545705538408559</v>
+        <v>0.7546494650912954</v>
       </c>
       <c r="G13" t="n">
-        <v>23.92824526519783</v>
+        <v>23.44704088387108</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71024547667937</v>
+        <v>34.71387539419956</v>
       </c>
       <c r="I13" t="n">
-        <v>2.287372492608523</v>
+        <v>2.293820417752666</v>
       </c>
       <c r="J13" t="n">
-        <v>4.71606596150535</v>
+        <v>4.716559156820596</v>
       </c>
       <c r="K13" t="n">
-        <v>22.14158303498376</v>
+        <v>22.78920856107503</v>
       </c>
       <c r="L13" t="n">
-        <v>41.67287421922845</v>
+        <v>41.68297694627097</v>
       </c>
       <c r="M13" t="n">
-        <v>99.9238288436834</v>
+        <v>99.92361496235732</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.22007462532974</v>
+        <v>83.74662679495671</v>
       </c>
       <c r="C14" t="n">
-        <v>40.06523792333316</v>
+        <v>39.50643810213764</v>
       </c>
       <c r="D14" t="n">
-        <v>1.550122209258699</v>
+        <v>1.518665507820971</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13065666395999</v>
+        <v>12.03763038193965</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554418171553744</v>
+        <v>0.7555357438834789</v>
       </c>
       <c r="G14" t="n">
-        <v>25.67527847627475</v>
+        <v>25.24100379581477</v>
       </c>
       <c r="H14" t="n">
-        <v>36.46972810178866</v>
+        <v>36.52107035220366</v>
       </c>
       <c r="I14" t="n">
-        <v>2.917335999671178</v>
+        <v>2.950622614022437</v>
       </c>
       <c r="J14" t="n">
-        <v>4.72151135722109</v>
+        <v>4.722098399271743</v>
       </c>
       <c r="K14" t="n">
-        <v>15.77992537467026</v>
+        <v>16.25337320504328</v>
       </c>
       <c r="L14" t="n">
-        <v>44.05770432237353</v>
+        <v>44.14194997963288</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90286762037695</v>
+        <v>99.90176128681381</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.53295922460444</v>
+        <v>83.01150393149376</v>
       </c>
       <c r="C15" t="n">
-        <v>39.8295693214334</v>
+        <v>39.22752126238791</v>
       </c>
       <c r="D15" t="n">
-        <v>1.524537691195137</v>
+        <v>1.491362664319912</v>
       </c>
       <c r="E15" t="n">
-        <v>12.33602114069285</v>
+        <v>12.23142940569312</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561753990899479</v>
+        <v>0.7562824623871475</v>
       </c>
       <c r="G15" t="n">
-        <v>25.2515121293121</v>
+        <v>24.78721645890765</v>
       </c>
       <c r="H15" t="n">
-        <v>36.50514252165097</v>
+        <v>36.55716521499016</v>
       </c>
       <c r="I15" t="n">
-        <v>2.433474098351272</v>
+        <v>2.461282335276076</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726096244312175</v>
+        <v>4.726765389919671</v>
       </c>
       <c r="K15" t="n">
-        <v>16.46704077539556</v>
+        <v>16.98849606850625</v>
       </c>
       <c r="L15" t="n">
-        <v>43.62235279206907</v>
+        <v>43.70202092982743</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91896288889802</v>
+        <v>99.91803826072159</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.15037535612194</v>
+        <v>80.6035713372876</v>
       </c>
       <c r="C16" t="n">
-        <v>37.82364500546744</v>
+        <v>37.20020316589003</v>
       </c>
       <c r="D16" t="n">
-        <v>1.432861211015368</v>
+        <v>1.399298463785283</v>
       </c>
       <c r="E16" t="n">
-        <v>11.93247168698341</v>
+        <v>11.8184986940282</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568058019097975</v>
+        <v>0.7569244951773856</v>
       </c>
       <c r="G16" t="n">
-        <v>23.7330388474759</v>
+        <v>23.25706197578684</v>
       </c>
       <c r="H16" t="n">
-        <v>36.53557586398445</v>
+        <v>36.58819978203816</v>
       </c>
       <c r="I16" t="n">
-        <v>2.029585682816767</v>
+        <v>2.052809831613077</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730036261936235</v>
+        <v>4.73077809485866</v>
       </c>
       <c r="K16" t="n">
-        <v>18.84962464387806</v>
+        <v>19.3964286627124</v>
       </c>
       <c r="L16" t="n">
-        <v>43.25913384792253</v>
+        <v>43.3349992176399</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93240349726804</v>
+        <v>99.93163104624233</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.6590957755773</v>
+        <v>82.22785327900986</v>
       </c>
       <c r="C17" t="n">
-        <v>38.94074466238009</v>
+        <v>38.38461190483531</v>
       </c>
       <c r="D17" t="n">
-        <v>1.434023847898792</v>
+        <v>1.400462490736733</v>
       </c>
       <c r="E17" t="n">
-        <v>12.65305367580645</v>
+        <v>12.57622983668845</v>
       </c>
       <c r="F17" t="n">
-        <v>0.757419881160548</v>
+        <v>0.7575541539209645</v>
       </c>
       <c r="G17" t="n">
-        <v>24.12784413909951</v>
+        <v>23.68229622591232</v>
       </c>
       <c r="H17" t="n">
-        <v>36.94076925294949</v>
+        <v>37.02452373468357</v>
       </c>
       <c r="I17" t="n">
-        <v>2.01211072140909</v>
+        <v>2.052073375061794</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733874257253426</v>
+        <v>4.734713462006027</v>
       </c>
       <c r="K17" t="n">
-        <v>17.34090422442269</v>
+        <v>17.77214672099014</v>
       </c>
       <c r="L17" t="n">
-        <v>43.65133513320498</v>
+        <v>43.77489578262196</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93298402000777</v>
+        <v>99.93165440844741</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.36667561625286</v>
+        <v>79.80844405414106</v>
       </c>
       <c r="C18" t="n">
-        <v>36.95938120705875</v>
+        <v>36.28214367337048</v>
       </c>
       <c r="D18" t="n">
-        <v>1.348938382090825</v>
+        <v>1.311426166271538</v>
       </c>
       <c r="E18" t="n">
-        <v>12.18195968720449</v>
+        <v>12.06189266952352</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579470044579693</v>
+        <v>0.7580956128554477</v>
       </c>
       <c r="G18" t="n">
-        <v>22.69625786490652</v>
+        <v>22.17666174816067</v>
       </c>
       <c r="H18" t="n">
-        <v>36.9664780316365</v>
+        <v>37.05098687143408</v>
       </c>
       <c r="I18" t="n">
-        <v>1.677925868094245</v>
+        <v>1.711283405549249</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737168777862308</v>
+        <v>4.738097580346547</v>
       </c>
       <c r="K18" t="n">
-        <v>19.63332438374716</v>
+        <v>20.19155594585894</v>
       </c>
       <c r="L18" t="n">
-        <v>43.35140244471049</v>
+        <v>43.46929834257443</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94410803551639</v>
+        <v>99.94299796180384</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.38870764066738</v>
+        <v>78.78261587797357</v>
       </c>
       <c r="C19" t="n">
-        <v>36.24018022253188</v>
+        <v>35.51992627141441</v>
       </c>
       <c r="D19" t="n">
-        <v>1.313294232456771</v>
+        <v>1.274352644530625</v>
       </c>
       <c r="E19" t="n">
-        <v>12.09324753463009</v>
+        <v>11.9587292725862</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583922559939145</v>
+        <v>0.7585533067795768</v>
       </c>
       <c r="G19" t="n">
-        <v>22.09653528142136</v>
+        <v>21.54973590772332</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98819377300794</v>
+        <v>37.07335609674877</v>
       </c>
       <c r="I19" t="n">
-        <v>1.399092963195322</v>
+        <v>1.426930482232718</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739951599961966</v>
+        <v>4.740958167372354</v>
       </c>
       <c r="K19" t="n">
-        <v>20.61129235933262</v>
+        <v>21.21738412202643</v>
       </c>
       <c r="L19" t="n">
-        <v>43.10191836624401</v>
+        <v>43.215153956405</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95339094810852</v>
+        <v>99.95246434984585</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.82228169708762</v>
+        <v>76.23096523734273</v>
       </c>
       <c r="C20" t="n">
-        <v>33.88936182803283</v>
+        <v>33.18790528018786</v>
       </c>
       <c r="D20" t="n">
-        <v>1.218976245923488</v>
+        <v>1.181481074213644</v>
       </c>
       <c r="E20" t="n">
-        <v>11.41915314909808</v>
+        <v>11.28549547635213</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587761139270067</v>
+        <v>0.7589479284001603</v>
       </c>
       <c r="G20" t="n">
-        <v>20.50960931647092</v>
+        <v>19.97924612041359</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00691523475588</v>
+        <v>37.09264274111855</v>
       </c>
       <c r="I20" t="n">
-        <v>1.166500924868452</v>
+        <v>1.189727344343662</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742350712043793</v>
+        <v>4.743424552501001</v>
       </c>
       <c r="K20" t="n">
-        <v>23.17771830291237</v>
+        <v>23.76903476265727</v>
       </c>
       <c r="L20" t="n">
-        <v>42.89405617563268</v>
+        <v>43.00342299931506</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96113630657788</v>
+        <v>99.9603630421602</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.39283598070851</v>
+        <v>81.94750540458514</v>
       </c>
       <c r="C21" t="n">
-        <v>37.32594318176064</v>
+        <v>36.75291095855872</v>
       </c>
       <c r="D21" t="n">
-        <v>1.219811504361677</v>
+        <v>1.182283262303426</v>
       </c>
       <c r="E21" t="n">
-        <v>13.27900501582408</v>
+        <v>13.20733192765121</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592960372265566</v>
+        <v>0.7594632299163804</v>
       </c>
       <c r="G21" t="n">
-        <v>22.09340684792953</v>
+        <v>21.6287865968434</v>
       </c>
       <c r="H21" t="n">
-        <v>38.60201693561213</v>
+        <v>38.75380266981423</v>
       </c>
       <c r="I21" t="n">
-        <v>1.693699407088559</v>
+        <v>1.669192531079106</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745600232665979</v>
+        <v>4.746645186977377</v>
       </c>
       <c r="K21" t="n">
-        <v>17.60716401929147</v>
+        <v>18.05249459541486</v>
       </c>
       <c r="L21" t="n">
-        <v>45.01047481038727</v>
+        <v>45.13899244698022</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94358201143939</v>
+        <v>99.9443980009538</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.05906166705924</v>
+        <v>45.53998774995101</v>
       </c>
       <c r="M2" t="n">
-        <v>100.8718419923032</v>
+        <v>99.69586869287363</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04584880523784</v>
+        <v>87.96431465840016</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93959165392831</v>
+        <v>45.90052798095326</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228769893903327</v>
+        <v>2.228590282907614</v>
       </c>
       <c r="E3" t="n">
-        <v>5.713579121241905</v>
+        <v>5.686815920154403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429232979677758</v>
+        <v>0.7428634276358715</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97671886042365</v>
+        <v>33.96400980208607</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17447170651768</v>
+        <v>34.17171767125009</v>
       </c>
       <c r="I3" t="n">
-        <v>6.566115312884911</v>
+        <v>6.52742113164191</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643270612298599</v>
+        <v>4.642896422724197</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95415119476215</v>
+        <v>12.03568534159985</v>
       </c>
       <c r="L3" t="n">
-        <v>48.87057143675116</v>
+        <v>48.82947097817441</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7643142854416</v>
+        <v>106.7656843007275</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.13159293506162</v>
+        <v>86.98561737524093</v>
       </c>
       <c r="C4" t="n">
-        <v>42.65969576348334</v>
+        <v>42.55016841790835</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184733660509007</v>
+        <v>2.181055744477826</v>
       </c>
       <c r="E4" t="n">
-        <v>6.514563184319801</v>
+        <v>6.473999384410079</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444817175186899</v>
+        <v>0.7444151244567927</v>
       </c>
       <c r="G4" t="n">
-        <v>33.3054038333302</v>
+        <v>33.23957716790058</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24615900585972</v>
+        <v>34.24309572501246</v>
       </c>
       <c r="I4" t="n">
-        <v>5.483240799032392</v>
+        <v>5.450879701128248</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653010734491811</v>
+        <v>4.652594527854954</v>
       </c>
       <c r="K4" t="n">
-        <v>12.86840706493838</v>
+        <v>13.01438262475906</v>
       </c>
       <c r="L4" t="n">
-        <v>44.28950507955371</v>
+        <v>44.25413170367587</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81760790797543</v>
+        <v>99.81868274634328</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.01325471961869</v>
+        <v>85.63932900241595</v>
       </c>
       <c r="C5" t="n">
-        <v>42.39240540232259</v>
+        <v>42.04982567357696</v>
       </c>
       <c r="D5" t="n">
-        <v>2.130339452546928</v>
+        <v>2.114706165304951</v>
       </c>
       <c r="E5" t="n">
-        <v>7.115279625639134</v>
+        <v>7.035462308089765</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458023841460784</v>
+        <v>0.7457336075231362</v>
       </c>
       <c r="G5" t="n">
-        <v>32.47618556516423</v>
+        <v>32.22840083159721</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30690967071959</v>
+        <v>34.30374594606426</v>
       </c>
       <c r="I5" t="n">
-        <v>4.577473120489739</v>
+        <v>4.550445096817009</v>
       </c>
       <c r="J5" t="n">
-        <v>4.66126490091299</v>
+        <v>4.660835047019601</v>
       </c>
       <c r="K5" t="n">
-        <v>13.98674528038131</v>
+        <v>14.36067099758407</v>
       </c>
       <c r="L5" t="n">
-        <v>43.46853707287853</v>
+        <v>43.43809000380762</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84768775558244</v>
+        <v>99.84858667496864</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.74487908988827</v>
+        <v>84.08675829310995</v>
       </c>
       <c r="C6" t="n">
-        <v>41.83499155338953</v>
+        <v>41.20373846665589</v>
       </c>
       <c r="D6" t="n">
-        <v>2.068679326351935</v>
+        <v>2.038424207434765</v>
       </c>
       <c r="E6" t="n">
-        <v>7.546051860999356</v>
+        <v>7.414635930765388</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469230747065323</v>
+        <v>0.7468563000114268</v>
       </c>
       <c r="G6" t="n">
-        <v>31.53620123642922</v>
+        <v>31.06585373413564</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35846143650047</v>
+        <v>34.35538980052563</v>
       </c>
       <c r="I6" t="n">
-        <v>3.820292937984926</v>
+        <v>3.797746445165688</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668269216915826</v>
+        <v>4.667851875071417</v>
       </c>
       <c r="K6" t="n">
-        <v>15.25512091011173</v>
+        <v>15.91324170689005</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78273550537403</v>
+        <v>42.7566185737647</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87284796887529</v>
+        <v>99.87359874731065</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.2424886191164</v>
+        <v>82.35806144233425</v>
       </c>
       <c r="C7" t="n">
-        <v>40.92606126910194</v>
+        <v>40.06453810562231</v>
       </c>
       <c r="D7" t="n">
-        <v>1.995697512399048</v>
+        <v>1.953959821601826</v>
       </c>
       <c r="E7" t="n">
-        <v>7.81110502183174</v>
+        <v>7.635543485523793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478764831342606</v>
+        <v>0.747814179878903</v>
       </c>
       <c r="G7" t="n">
-        <v>30.423622238757</v>
+        <v>29.77860535548152</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40231822417597</v>
+        <v>34.39945227442954</v>
       </c>
       <c r="I7" t="n">
-        <v>3.187641119229249</v>
+        <v>3.168847701175522</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674228019589128</v>
+        <v>4.673838624243143</v>
       </c>
       <c r="K7" t="n">
-        <v>16.75751138088362</v>
+        <v>17.64193855766574</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21030810173706</v>
+        <v>42.18803037990179</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89388075172261</v>
+        <v>99.89450704318985</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.11653566089227</v>
+        <v>87.24893650854541</v>
       </c>
       <c r="C8" t="n">
-        <v>43.19490628831993</v>
+        <v>42.32179681892502</v>
       </c>
       <c r="D8" t="n">
-        <v>1.999977047526031</v>
+        <v>1.958197970986872</v>
       </c>
       <c r="E8" t="n">
-        <v>9.623686178935808</v>
+        <v>9.441283062431554</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494802149925873</v>
+        <v>0.7494361928658356</v>
       </c>
       <c r="G8" t="n">
-        <v>30.91438916804852</v>
+        <v>30.26467579805871</v>
       </c>
       <c r="H8" t="n">
-        <v>34.476089889659</v>
+        <v>34.47406487182844</v>
       </c>
       <c r="I8" t="n">
-        <v>5.668661818026659</v>
+        <v>5.67730240696253</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684251343703671</v>
+        <v>4.683976205411472</v>
       </c>
       <c r="K8" t="n">
-        <v>11.88346433910772</v>
+        <v>12.75106349145459</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73307830390117</v>
+        <v>44.73830585765432</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81144893132881</v>
+        <v>99.81116616803392</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.16395643776313</v>
+        <v>85.10476812441053</v>
       </c>
       <c r="C9" t="n">
-        <v>42.12226752776638</v>
+        <v>41.05793886339734</v>
       </c>
       <c r="D9" t="n">
-        <v>1.911667749480626</v>
+        <v>1.860871227887562</v>
       </c>
       <c r="E9" t="n">
-        <v>9.98750639245179</v>
+        <v>9.762008630161946</v>
       </c>
       <c r="F9" t="n">
-        <v>0.750852382016712</v>
+        <v>0.7508275089648703</v>
       </c>
       <c r="G9" t="n">
-        <v>29.54935949917811</v>
+        <v>28.76045489188696</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53920957276874</v>
+        <v>34.53806541238404</v>
       </c>
       <c r="I9" t="n">
-        <v>4.732533454262698</v>
+        <v>4.739868522094721</v>
       </c>
       <c r="J9" t="n">
-        <v>4.69282738760445</v>
+        <v>4.692671931030439</v>
       </c>
       <c r="K9" t="n">
-        <v>13.83604356223687</v>
+        <v>14.89523187558947</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88422608171822</v>
+        <v>43.88912641637535</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84253717172147</v>
+        <v>99.84229715536216</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.11511048306014</v>
+        <v>82.77511331947922</v>
       </c>
       <c r="C10" t="n">
-        <v>40.8078363815163</v>
+        <v>39.46282252648317</v>
       </c>
       <c r="D10" t="n">
-        <v>1.82001635180852</v>
+        <v>1.756313933723605</v>
       </c>
       <c r="E10" t="n">
-        <v>10.16699892621762</v>
+        <v>9.8728717743471</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520276881511894</v>
+        <v>0.7520236861917046</v>
       </c>
       <c r="G10" t="n">
-        <v>28.13266975319533</v>
+        <v>27.14448313771357</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59327365495469</v>
+        <v>34.59308956481841</v>
       </c>
       <c r="I10" t="n">
-        <v>3.949951057787864</v>
+        <v>3.956183183986663</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700173050944933</v>
+        <v>4.700148038698154</v>
       </c>
       <c r="K10" t="n">
-        <v>15.88488951693985</v>
+        <v>17.2248866805208</v>
       </c>
       <c r="L10" t="n">
-        <v>43.17581483892544</v>
+        <v>43.18062777849341</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86854073738159</v>
+        <v>99.86833698549736</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.92143778798432</v>
+        <v>80.28521493738353</v>
       </c>
       <c r="C11" t="n">
-        <v>39.22664433787847</v>
+        <v>37.58526403654512</v>
       </c>
       <c r="D11" t="n">
-        <v>1.722808540226829</v>
+        <v>1.645782833621482</v>
       </c>
       <c r="E11" t="n">
-        <v>10.17331545772734</v>
+        <v>9.801759769005919</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530362616151334</v>
+        <v>0.7530544631556706</v>
       </c>
       <c r="G11" t="n">
-        <v>26.63009245055676</v>
+        <v>25.43618399750577</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63966803429611</v>
+        <v>34.64050530516085</v>
       </c>
       <c r="I11" t="n">
-        <v>3.296040408467562</v>
+        <v>3.301338174210901</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706476635094583</v>
+        <v>4.706590394722941</v>
       </c>
       <c r="K11" t="n">
-        <v>18.07856221201568</v>
+        <v>19.71478506261647</v>
       </c>
       <c r="L11" t="n">
-        <v>42.58507258738951</v>
+        <v>42.59005692350545</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89027913728366</v>
+        <v>99.89010602266704</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.6478950104985</v>
+        <v>77.75048279128259</v>
       </c>
       <c r="C12" t="n">
-        <v>37.46349332270519</v>
+        <v>35.56056810805053</v>
       </c>
       <c r="D12" t="n">
-        <v>1.623006330766918</v>
+        <v>1.53449083368863</v>
       </c>
       <c r="E12" t="n">
-        <v>10.04228604629545</v>
+        <v>9.598000605674834</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539028864495828</v>
+        <v>0.7539437120668081</v>
       </c>
       <c r="G12" t="n">
-        <v>25.08741257485952</v>
+        <v>23.7161248682504</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67953277668079</v>
+        <v>34.68141075507318</v>
       </c>
       <c r="I12" t="n">
-        <v>2.749861355136345</v>
+        <v>2.754363816111197</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711893040309892</v>
+        <v>4.71214820041755</v>
       </c>
       <c r="K12" t="n">
-        <v>20.35210498950149</v>
+        <v>22.24951720871741</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09284500978033</v>
+        <v>42.09821084505954</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90844332198702</v>
+        <v>99.90829616182748</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.21079143892497</v>
+        <v>75.12051151418861</v>
       </c>
       <c r="C13" t="n">
-        <v>35.45142945501132</v>
+        <v>33.35513927260214</v>
       </c>
       <c r="D13" t="n">
-        <v>1.516884042095624</v>
+        <v>1.420131580719597</v>
       </c>
       <c r="E13" t="n">
-        <v>9.767962079094138</v>
+        <v>9.265641885980104</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546494650912954</v>
+        <v>0.7547123852751679</v>
       </c>
       <c r="G13" t="n">
-        <v>23.44704088387108</v>
+        <v>21.94866020589467</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71387539419956</v>
+        <v>34.71676972265773</v>
       </c>
       <c r="I13" t="n">
-        <v>2.293820417752666</v>
+        <v>2.297643325691549</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716559156820596</v>
+        <v>4.716952407969798</v>
       </c>
       <c r="K13" t="n">
-        <v>22.78920856107503</v>
+        <v>24.87948848581139</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68297694627097</v>
+        <v>41.6888621355834</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92361496235732</v>
+        <v>99.92348989399693</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.74662679495671</v>
+        <v>82.41993221734573</v>
       </c>
       <c r="C14" t="n">
-        <v>39.50643810213764</v>
+        <v>37.87955458402553</v>
       </c>
       <c r="D14" t="n">
-        <v>1.518665507820971</v>
+        <v>1.421863657703097</v>
       </c>
       <c r="E14" t="n">
-        <v>12.03763038193965</v>
+        <v>11.77619609671777</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555357438834789</v>
+        <v>0.7556328774108583</v>
       </c>
       <c r="G14" t="n">
-        <v>25.24100379581477</v>
+        <v>23.97206211106006</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52107035220366</v>
+        <v>36.75574437398063</v>
       </c>
       <c r="I14" t="n">
-        <v>2.950622614022437</v>
+        <v>3.015727616655451</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722098399271743</v>
+        <v>4.722705483817863</v>
       </c>
       <c r="K14" t="n">
-        <v>16.25337320504328</v>
+        <v>17.58006778265425</v>
       </c>
       <c r="L14" t="n">
-        <v>44.14194997963288</v>
+        <v>44.43997583543901</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90176128681381</v>
+        <v>99.8995982021188</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.01150393149376</v>
+        <v>81.57324354477218</v>
       </c>
       <c r="C15" t="n">
-        <v>39.22752126238791</v>
+        <v>37.49791712818703</v>
       </c>
       <c r="D15" t="n">
-        <v>1.491362664319912</v>
+        <v>1.390903754336683</v>
       </c>
       <c r="E15" t="n">
-        <v>12.23142940569312</v>
+        <v>11.93906081313833</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562824623871475</v>
+        <v>0.756409659041953</v>
       </c>
       <c r="G15" t="n">
-        <v>24.78721645890765</v>
+        <v>23.45009031550056</v>
       </c>
       <c r="H15" t="n">
-        <v>36.55716521499016</v>
+        <v>36.79352884302696</v>
       </c>
       <c r="I15" t="n">
-        <v>2.461282335276076</v>
+        <v>2.515689790715482</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726765389919671</v>
+        <v>4.727560369012204</v>
       </c>
       <c r="K15" t="n">
-        <v>16.98849606850625</v>
+        <v>18.42675645522783</v>
       </c>
       <c r="L15" t="n">
-        <v>43.70202092982743</v>
+        <v>43.99155620501137</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91803826072159</v>
+        <v>99.91622978842622</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.6035713372876</v>
+        <v>78.87243597543511</v>
       </c>
       <c r="C16" t="n">
-        <v>37.20020316589003</v>
+        <v>35.18505833250205</v>
       </c>
       <c r="D16" t="n">
-        <v>1.399298463785283</v>
+        <v>1.289910720529625</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8184986940282</v>
+        <v>11.421880995385</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7569244951773856</v>
+        <v>0.7570804255192383</v>
       </c>
       <c r="G16" t="n">
-        <v>23.25706197578684</v>
+        <v>21.74738748172947</v>
       </c>
       <c r="H16" t="n">
-        <v>36.58819978203816</v>
+        <v>36.82615648789362</v>
       </c>
       <c r="I16" t="n">
-        <v>2.052809831613077</v>
+        <v>2.098267204882919</v>
       </c>
       <c r="J16" t="n">
-        <v>4.73077809485866</v>
+        <v>4.731752659495237</v>
       </c>
       <c r="K16" t="n">
-        <v>19.3964286627124</v>
+        <v>21.12756402456489</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3349992176399</v>
+        <v>43.61749737096874</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93163104624233</v>
+        <v>99.93011972803568</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.22785327900986</v>
+        <v>80.77029173242281</v>
       </c>
       <c r="C17" t="n">
-        <v>38.38461190483531</v>
+        <v>36.55128125179431</v>
       </c>
       <c r="D17" t="n">
-        <v>1.400462490736733</v>
+        <v>1.291028806970894</v>
       </c>
       <c r="E17" t="n">
-        <v>12.57622983668845</v>
+        <v>12.27489876096895</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7575541539209645</v>
+        <v>0.7577366580361489</v>
       </c>
       <c r="G17" t="n">
-        <v>23.68229622591232</v>
+        <v>22.25929944486345</v>
       </c>
       <c r="H17" t="n">
-        <v>37.02452373468357</v>
+        <v>37.35113863248163</v>
       </c>
       <c r="I17" t="n">
-        <v>2.052073375061794</v>
+        <v>2.100335316375789</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734713462006027</v>
+        <v>4.735854112725928</v>
       </c>
       <c r="K17" t="n">
-        <v>17.77214672099014</v>
+        <v>19.22970826757721</v>
       </c>
       <c r="L17" t="n">
-        <v>43.77489578262196</v>
+        <v>44.14905993610482</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93165440844741</v>
+        <v>99.93004945547634</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.80844405414106</v>
+        <v>78.1836516036126</v>
       </c>
       <c r="C18" t="n">
-        <v>36.28214367337048</v>
+        <v>34.28803678041478</v>
       </c>
       <c r="D18" t="n">
-        <v>1.311426166271538</v>
+        <v>1.198708917720177</v>
       </c>
       <c r="E18" t="n">
-        <v>12.06189266952352</v>
+        <v>11.68906686481351</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7580956128554477</v>
+        <v>0.7583025228431189</v>
       </c>
       <c r="G18" t="n">
-        <v>22.17666174816067</v>
+        <v>20.66756419584924</v>
       </c>
       <c r="H18" t="n">
-        <v>37.05098687143408</v>
+        <v>37.37903182549034</v>
       </c>
       <c r="I18" t="n">
-        <v>1.711283405549249</v>
+        <v>1.751586509126719</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738097580346547</v>
+        <v>4.739390767769491</v>
       </c>
       <c r="K18" t="n">
-        <v>20.19155594585894</v>
+        <v>21.81634839638741</v>
       </c>
       <c r="L18" t="n">
-        <v>43.46929834257443</v>
+        <v>43.83727217552071</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94299796180384</v>
+        <v>99.94165735232289</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.78261587797357</v>
+        <v>77.18853249563392</v>
       </c>
       <c r="C19" t="n">
-        <v>35.51992627141441</v>
+        <v>33.5576906831505</v>
       </c>
       <c r="D19" t="n">
-        <v>1.274352644530625</v>
+        <v>1.163725033020162</v>
       </c>
       <c r="E19" t="n">
-        <v>11.9587292725862</v>
+        <v>11.59201855570486</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585533067795768</v>
+        <v>0.7587821180090178</v>
       </c>
       <c r="G19" t="n">
-        <v>21.54973590772332</v>
+        <v>20.06438883595213</v>
       </c>
       <c r="H19" t="n">
-        <v>37.07335609674877</v>
+        <v>37.40267252617306</v>
       </c>
       <c r="I19" t="n">
-        <v>1.426930482232718</v>
+        <v>1.464557189218342</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740958167372354</v>
+        <v>4.74238823755636</v>
       </c>
       <c r="K19" t="n">
-        <v>21.21738412202643</v>
+        <v>22.81146750436606</v>
       </c>
       <c r="L19" t="n">
-        <v>43.215153956405</v>
+        <v>43.5820540957343</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95246434984585</v>
+        <v>99.95121228325085</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.23096523734273</v>
+        <v>74.60235378824473</v>
       </c>
       <c r="C20" t="n">
-        <v>33.18790528018786</v>
+        <v>31.19614655602174</v>
       </c>
       <c r="D20" t="n">
-        <v>1.181481074213644</v>
+        <v>1.072610108309795</v>
       </c>
       <c r="E20" t="n">
-        <v>11.28549547635213</v>
+        <v>10.88793247725046</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589479284001603</v>
+        <v>0.7591961227224153</v>
       </c>
       <c r="G20" t="n">
-        <v>19.97924612041359</v>
+        <v>18.49342900757862</v>
       </c>
       <c r="H20" t="n">
-        <v>37.09264274111855</v>
+        <v>37.42308007446918</v>
       </c>
       <c r="I20" t="n">
-        <v>1.189727344343662</v>
+        <v>1.221130230899157</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743424552501001</v>
+        <v>4.744975767015093</v>
       </c>
       <c r="K20" t="n">
-        <v>23.76903476265727</v>
+        <v>25.39764621175527</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00342299931506</v>
+        <v>43.36552508807804</v>
       </c>
       <c r="M20" t="n">
-        <v>99.9603630421602</v>
+        <v>99.95931785585506</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.94750540458514</v>
+        <v>80.90978826371922</v>
       </c>
       <c r="C21" t="n">
-        <v>36.75291095855872</v>
+        <v>35.13888267526716</v>
       </c>
       <c r="D21" t="n">
-        <v>1.182283262303426</v>
+        <v>1.073373498797638</v>
       </c>
       <c r="E21" t="n">
-        <v>13.20733192765121</v>
+        <v>13.00389738748828</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594632299163804</v>
+        <v>0.7597364524228378</v>
       </c>
       <c r="G21" t="n">
-        <v>21.6287865968434</v>
+        <v>20.32688413386499</v>
       </c>
       <c r="H21" t="n">
-        <v>38.75380266981423</v>
+        <v>39.27000767826689</v>
       </c>
       <c r="I21" t="n">
-        <v>1.669192531079106</v>
+        <v>1.727536285235852</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746645186977377</v>
+        <v>4.748352827642734</v>
       </c>
       <c r="K21" t="n">
-        <v>18.05249459541486</v>
+        <v>19.09021173628078</v>
       </c>
       <c r="L21" t="n">
-        <v>45.13899244698022</v>
+        <v>45.71336200012696</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9443980009538</v>
+        <v>99.94245641167491</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_21_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.53998774995101</v>
+        <v>44.08746267366342</v>
       </c>
       <c r="M2" t="n">
-        <v>99.69586869287363</v>
+        <v>93.23307629461743</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.96431465840016</v>
+        <v>81.42772458627421</v>
       </c>
       <c r="C3" t="n">
-        <v>45.90052798095326</v>
+        <v>43.18328014182978</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228590282907614</v>
+        <v>2.177792224585191</v>
       </c>
       <c r="E3" t="n">
-        <v>5.686815920154403</v>
+        <v>4.141874715559983</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428634276358715</v>
+        <v>0.7375982514019179</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96400980208607</v>
+        <v>32.75762471146891</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17171767125009</v>
+        <v>33.92951956448822</v>
       </c>
       <c r="I3" t="n">
-        <v>6.52742113164191</v>
+        <v>3.073326047507991</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642896422724197</v>
+        <v>4.609989071261987</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03568534159985</v>
+        <v>18.57227541372579</v>
       </c>
       <c r="L3" t="n">
-        <v>48.82947097817441</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7656843007275</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>86.98561737524093</v>
+        <v>88.31850839144192</v>
       </c>
       <c r="C4" t="n">
-        <v>42.55016841790835</v>
+        <v>42.74359384972299</v>
       </c>
       <c r="D4" t="n">
-        <v>2.181055744477826</v>
+        <v>2.183402828469926</v>
       </c>
       <c r="E4" t="n">
-        <v>6.473999384410079</v>
+        <v>6.489266855075054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444151244567927</v>
+        <v>0.7394985114763049</v>
       </c>
       <c r="G4" t="n">
-        <v>33.23957716790058</v>
+        <v>33.44154514681556</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24309572501246</v>
+        <v>34.01693152791002</v>
       </c>
       <c r="I4" t="n">
-        <v>5.450879701128248</v>
+        <v>6.825997824968169</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652594527854954</v>
+        <v>4.621865696726905</v>
       </c>
       <c r="K4" t="n">
-        <v>13.01438262475906</v>
+        <v>11.68149160855807</v>
       </c>
       <c r="L4" t="n">
-        <v>44.25413170367587</v>
+        <v>45.34796596410703</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81868274634328</v>
+        <v>99.77305142238809</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.63932900241595</v>
+        <v>86.88915045427485</v>
       </c>
       <c r="C5" t="n">
-        <v>42.04982567357696</v>
+        <v>42.37241065813757</v>
       </c>
       <c r="D5" t="n">
-        <v>2.114706165304951</v>
+        <v>2.113911073810941</v>
       </c>
       <c r="E5" t="n">
-        <v>7.035462308089765</v>
+        <v>7.232859838013729</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457336075231362</v>
+        <v>0.7411157875392681</v>
       </c>
       <c r="G5" t="n">
-        <v>32.22840083159721</v>
+        <v>32.37719200938356</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30374594606426</v>
+        <v>34.09132622680632</v>
       </c>
       <c r="I5" t="n">
-        <v>4.550445096817009</v>
+        <v>5.700771846600614</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660835047019601</v>
+        <v>4.631973672120425</v>
       </c>
       <c r="K5" t="n">
-        <v>14.36067099758407</v>
+        <v>13.11084954572515</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43809000380762</v>
+        <v>44.32712874544373</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84858667496864</v>
+        <v>99.81038894930644</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.08675829310995</v>
+        <v>84.99962406231856</v>
       </c>
       <c r="C6" t="n">
-        <v>41.20373846665589</v>
+        <v>41.36732618437459</v>
       </c>
       <c r="D6" t="n">
-        <v>2.038424207434765</v>
+        <v>2.021946634452051</v>
       </c>
       <c r="E6" t="n">
-        <v>7.414635930765388</v>
+        <v>7.711450288367027</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468563000114268</v>
+        <v>0.742499067441481</v>
       </c>
       <c r="G6" t="n">
-        <v>31.06585373413564</v>
+        <v>30.96864159870322</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35538980052563</v>
+        <v>34.15495710230812</v>
       </c>
       <c r="I6" t="n">
-        <v>3.797746445165688</v>
+        <v>4.759510199537399</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667851875071417</v>
+        <v>4.640619171509256</v>
       </c>
       <c r="K6" t="n">
-        <v>15.91324170689005</v>
+        <v>15.00037593768147</v>
       </c>
       <c r="L6" t="n">
-        <v>42.7566185737647</v>
+        <v>43.47394310442726</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87359874731065</v>
+        <v>99.84164522648331</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.35806144233425</v>
+        <v>82.86706304655004</v>
       </c>
       <c r="C7" t="n">
-        <v>40.06453810562231</v>
+        <v>39.97301965646437</v>
       </c>
       <c r="D7" t="n">
-        <v>1.953959821601826</v>
+        <v>1.919069589581215</v>
       </c>
       <c r="E7" t="n">
-        <v>7.635543485523793</v>
+        <v>7.981189588413317</v>
       </c>
       <c r="F7" t="n">
-        <v>0.747814179878903</v>
+        <v>0.7436855658676835</v>
       </c>
       <c r="G7" t="n">
-        <v>29.77860535548152</v>
+        <v>29.39295098597742</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39945227442954</v>
+        <v>34.20953602991344</v>
       </c>
       <c r="I7" t="n">
-        <v>3.168847701175522</v>
+        <v>3.972596500123942</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673838624243143</v>
+        <v>4.648034786673022</v>
       </c>
       <c r="K7" t="n">
-        <v>17.64193855766574</v>
+        <v>17.13293695344996</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18803037990179</v>
+        <v>42.76183477343187</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89450704318985</v>
+        <v>99.8677913833462</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.24893650854541</v>
+        <v>80.63426535714737</v>
       </c>
       <c r="C8" t="n">
-        <v>42.32179681892502</v>
+        <v>38.35584755434306</v>
       </c>
       <c r="D8" t="n">
-        <v>1.958197970986872</v>
+        <v>1.812500814147751</v>
       </c>
       <c r="E8" t="n">
-        <v>9.441283062431554</v>
+        <v>8.090487945614626</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494361928658356</v>
+        <v>0.7447047119118151</v>
       </c>
       <c r="G8" t="n">
-        <v>30.26467579805871</v>
+        <v>27.76071690235828</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47406487182844</v>
+        <v>34.25641674794349</v>
       </c>
       <c r="I8" t="n">
-        <v>5.67730240696253</v>
+        <v>3.31503378572256</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683976205411472</v>
+        <v>4.654404449448844</v>
       </c>
       <c r="K8" t="n">
-        <v>12.75106349145459</v>
+        <v>19.36573464285264</v>
       </c>
       <c r="L8" t="n">
-        <v>44.73830585765432</v>
+        <v>42.16806790002308</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81116616803392</v>
+        <v>99.88965009721878</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.10476812441053</v>
+        <v>78.19559088231669</v>
       </c>
       <c r="C9" t="n">
-        <v>41.05793886339734</v>
+        <v>36.43015725832996</v>
       </c>
       <c r="D9" t="n">
-        <v>1.860871227887562</v>
+        <v>1.69714239477221</v>
       </c>
       <c r="E9" t="n">
-        <v>9.762008630161946</v>
+        <v>8.0365249803565</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508275089648703</v>
+        <v>0.745582721031988</v>
       </c>
       <c r="G9" t="n">
-        <v>28.76045489188696</v>
+        <v>25.99385842836983</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53806541238404</v>
+        <v>34.29680516747144</v>
       </c>
       <c r="I9" t="n">
-        <v>4.739868522094721</v>
+        <v>2.765785183864795</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692671931030439</v>
+        <v>4.659892006449924</v>
       </c>
       <c r="K9" t="n">
-        <v>14.89523187558947</v>
+        <v>21.80440911768329</v>
       </c>
       <c r="L9" t="n">
-        <v>43.88912641637535</v>
+        <v>41.67334935216114</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84229715536216</v>
+        <v>99.90791572817439</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.77511331947922</v>
+        <v>84.12650425163798</v>
       </c>
       <c r="C10" t="n">
-        <v>39.46282252648317</v>
+        <v>40.49160310821337</v>
       </c>
       <c r="D10" t="n">
-        <v>1.756313933723605</v>
+        <v>1.699033718274603</v>
       </c>
       <c r="E10" t="n">
-        <v>9.8728717743471</v>
+        <v>10.2913473595596</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520236861917046</v>
+        <v>0.7464136107249272</v>
       </c>
       <c r="G10" t="n">
-        <v>27.14448313771357</v>
+        <v>27.79993293062283</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59308956481841</v>
+        <v>36.11213261064157</v>
       </c>
       <c r="I10" t="n">
-        <v>3.956183183986663</v>
+        <v>2.812558954783662</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700148038698154</v>
+        <v>4.665085067030795</v>
       </c>
       <c r="K10" t="n">
-        <v>17.2248866805208</v>
+        <v>15.87349574836202</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18062777849341</v>
+        <v>43.54125354069962</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86833698549736</v>
+        <v>99.90635239727501</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.28521493738353</v>
+        <v>83.39250058055785</v>
       </c>
       <c r="C11" t="n">
-        <v>37.58526403654512</v>
+        <v>40.07570449138929</v>
       </c>
       <c r="D11" t="n">
-        <v>1.645782833621482</v>
+        <v>1.660134373661585</v>
       </c>
       <c r="E11" t="n">
-        <v>9.801759769005919</v>
+        <v>10.50131048954418</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530544631556706</v>
+        <v>0.7471353225839493</v>
       </c>
       <c r="G11" t="n">
-        <v>25.43618399750577</v>
+        <v>27.20587374796573</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64050530516085</v>
+        <v>36.18946940345054</v>
       </c>
       <c r="I11" t="n">
-        <v>3.301338174210901</v>
+        <v>2.418981477202173</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706590394722941</v>
+        <v>4.669595766149683</v>
       </c>
       <c r="K11" t="n">
-        <v>19.71478506261647</v>
+        <v>16.60749941944215</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59005692350545</v>
+        <v>43.23624126221385</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89010602266704</v>
+        <v>99.91944517304529</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.75048279128259</v>
+        <v>80.98927055785502</v>
       </c>
       <c r="C12" t="n">
-        <v>35.56056810805053</v>
+        <v>38.04719356066406</v>
       </c>
       <c r="D12" t="n">
-        <v>1.53449083368863</v>
+        <v>1.560083621650534</v>
       </c>
       <c r="E12" t="n">
-        <v>9.598000605674834</v>
+        <v>10.20468021554743</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539437120668081</v>
+        <v>0.7477557090174188</v>
       </c>
       <c r="G12" t="n">
-        <v>23.7161248682504</v>
+        <v>25.5662666349595</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68141075507318</v>
+        <v>36.21951945619696</v>
       </c>
       <c r="I12" t="n">
-        <v>2.754363816111197</v>
+        <v>2.017491739124312</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71214820041755</v>
+        <v>4.673473181358868</v>
       </c>
       <c r="K12" t="n">
-        <v>22.24951720871741</v>
+        <v>19.01072944214496</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09821084505954</v>
+        <v>42.8748830672687</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90829616182748</v>
+        <v>99.93280607007773</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.12051151418861</v>
+        <v>82.27548767761991</v>
       </c>
       <c r="C13" t="n">
-        <v>33.35513927260214</v>
+        <v>39.09992517725183</v>
       </c>
       <c r="D13" t="n">
-        <v>1.420131580719597</v>
+        <v>1.561263465896732</v>
       </c>
       <c r="E13" t="n">
-        <v>9.265641885980104</v>
+        <v>10.87890951619307</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7547123852751679</v>
+        <v>0.7483212141343257</v>
       </c>
       <c r="G13" t="n">
-        <v>21.94866020589467</v>
+        <v>25.94100107657062</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71676972265773</v>
+        <v>36.60231063199206</v>
       </c>
       <c r="I13" t="n">
-        <v>2.297643325691549</v>
+        <v>1.866674184493565</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716952407969798</v>
+        <v>4.677007588339536</v>
       </c>
       <c r="K13" t="n">
-        <v>24.87948848581139</v>
+        <v>17.72451232238009</v>
       </c>
       <c r="L13" t="n">
-        <v>41.6888621355834</v>
+        <v>43.11338704897249</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92348989399693</v>
+        <v>99.9378245486044</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.41993221734573</v>
+        <v>79.96403143031011</v>
       </c>
       <c r="C14" t="n">
-        <v>37.87955458402553</v>
+        <v>37.07729932888682</v>
       </c>
       <c r="D14" t="n">
-        <v>1.421863657703097</v>
+        <v>1.468190442735042</v>
       </c>
       <c r="E14" t="n">
-        <v>11.77619609671777</v>
+        <v>10.4898036874038</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556328774108583</v>
+        <v>0.7488067721219791</v>
       </c>
       <c r="G14" t="n">
-        <v>23.97206211106006</v>
+        <v>24.3945565162668</v>
       </c>
       <c r="H14" t="n">
-        <v>36.75574437398063</v>
+        <v>36.62606051901684</v>
       </c>
       <c r="I14" t="n">
-        <v>3.015727616655451</v>
+        <v>1.556571167003279</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722705483817863</v>
+        <v>4.680042325762369</v>
       </c>
       <c r="K14" t="n">
-        <v>17.58006778265425</v>
+        <v>20.0359685696899</v>
       </c>
       <c r="L14" t="n">
-        <v>44.43997583543901</v>
+        <v>42.8348800407429</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8995982021188</v>
+        <v>99.94814793931961</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.57324354477218</v>
+        <v>78.94587070371276</v>
       </c>
       <c r="C15" t="n">
-        <v>37.49791712818703</v>
+        <v>36.2578106619324</v>
       </c>
       <c r="D15" t="n">
-        <v>1.390903754336683</v>
+        <v>1.425924613086617</v>
       </c>
       <c r="E15" t="n">
-        <v>11.93906081313833</v>
+        <v>10.41084859840157</v>
       </c>
       <c r="F15" t="n">
-        <v>0.756409659041953</v>
+        <v>0.7492298482780787</v>
       </c>
       <c r="G15" t="n">
-        <v>23.45009031550056</v>
+        <v>23.69229328116176</v>
       </c>
       <c r="H15" t="n">
-        <v>36.79352884302696</v>
+        <v>36.64675425934393</v>
       </c>
       <c r="I15" t="n">
-        <v>2.515689790715482</v>
+        <v>1.338133551702807</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727560369012204</v>
+        <v>4.682686551737992</v>
       </c>
       <c r="K15" t="n">
-        <v>18.42675645522783</v>
+        <v>21.05412929628723</v>
       </c>
       <c r="L15" t="n">
-        <v>43.99155620501137</v>
+        <v>42.64348077736099</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91622978842622</v>
+        <v>99.95542073558063</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.87243597543511</v>
+        <v>76.39310087069907</v>
       </c>
       <c r="C16" t="n">
-        <v>35.18505833250205</v>
+        <v>33.91137839009529</v>
       </c>
       <c r="D16" t="n">
-        <v>1.289910720529625</v>
+        <v>1.324115943931391</v>
       </c>
       <c r="E16" t="n">
-        <v>11.421880995385</v>
+        <v>9.853473508739118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570804255192383</v>
+        <v>0.7495945764048588</v>
       </c>
       <c r="G16" t="n">
-        <v>21.74738748172947</v>
+        <v>22.00070255746348</v>
       </c>
       <c r="H16" t="n">
-        <v>36.82615648789362</v>
+        <v>36.66459404784715</v>
       </c>
       <c r="I16" t="n">
-        <v>2.098267204882919</v>
+        <v>1.115654133782707</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731752659495237</v>
+        <v>4.684966102530367</v>
       </c>
       <c r="K16" t="n">
-        <v>21.12756402456489</v>
+        <v>23.60689912930091</v>
       </c>
       <c r="L16" t="n">
-        <v>43.61749737096874</v>
+        <v>42.4445521041676</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93011972803568</v>
+        <v>99.96282962356381</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.77029173242281</v>
+        <v>82.1951316280273</v>
       </c>
       <c r="C17" t="n">
-        <v>36.55128125179431</v>
+        <v>37.77982469627743</v>
       </c>
       <c r="D17" t="n">
-        <v>1.291028806970894</v>
+        <v>1.324760508729814</v>
       </c>
       <c r="E17" t="n">
-        <v>12.27489876096895</v>
+        <v>11.88520583591571</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577366580361489</v>
+        <v>0.749959470641843</v>
       </c>
       <c r="G17" t="n">
-        <v>22.25929944486345</v>
+        <v>23.83828967614771</v>
       </c>
       <c r="H17" t="n">
-        <v>37.35113863248163</v>
+        <v>38.50931938452953</v>
       </c>
       <c r="I17" t="n">
-        <v>2.100335316375789</v>
+        <v>1.200350060551184</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735854112725928</v>
+        <v>4.687246691511518</v>
       </c>
       <c r="K17" t="n">
-        <v>19.22970826757721</v>
+        <v>17.80486837197269</v>
       </c>
       <c r="L17" t="n">
-        <v>44.14905993610482</v>
+        <v>44.37531473081994</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93004945547634</v>
+        <v>99.96000779907006</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>78.1836516036126</v>
+        <v>84.06136529146121</v>
       </c>
       <c r="C18" t="n">
-        <v>34.28803678041478</v>
+        <v>38.53819160172498</v>
       </c>
       <c r="D18" t="n">
-        <v>1.198708917720177</v>
+        <v>1.325944341359107</v>
       </c>
       <c r="E18" t="n">
-        <v>11.68906686481351</v>
+        <v>12.51478315065025</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583025228431189</v>
+        <v>0.7506296495052243</v>
       </c>
       <c r="G18" t="n">
-        <v>20.66756419584924</v>
+        <v>23.98127296316352</v>
       </c>
       <c r="H18" t="n">
-        <v>37.37903182549034</v>
+        <v>38.54373208668878</v>
       </c>
       <c r="I18" t="n">
-        <v>1.751586509126719</v>
+        <v>2.253567790686682</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739390767769491</v>
+        <v>4.691435309407652</v>
       </c>
       <c r="K18" t="n">
-        <v>21.81634839638741</v>
+        <v>15.9386347085388</v>
       </c>
       <c r="L18" t="n">
-        <v>43.83727217552071</v>
+        <v>45.44812183122991</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94165735232289</v>
+        <v>99.92494814149369</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>77.18853249563392</v>
+        <v>81.23919407092514</v>
       </c>
       <c r="C19" t="n">
-        <v>33.5576906831505</v>
+        <v>36.06345441062631</v>
       </c>
       <c r="D19" t="n">
-        <v>1.163725033020162</v>
+        <v>1.227952308941136</v>
       </c>
       <c r="E19" t="n">
-        <v>11.59201855570486</v>
+        <v>11.90313277717504</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587821180090178</v>
+        <v>0.7512084954704707</v>
       </c>
       <c r="G19" t="n">
-        <v>20.06438883595213</v>
+        <v>22.2089710615454</v>
       </c>
       <c r="H19" t="n">
-        <v>37.40267252617306</v>
+        <v>38.57345497842191</v>
       </c>
       <c r="I19" t="n">
-        <v>1.464557189218342</v>
+        <v>1.879421352680741</v>
       </c>
       <c r="J19" t="n">
-        <v>4.74238823755636</v>
+        <v>4.695053096690442</v>
       </c>
       <c r="K19" t="n">
-        <v>22.81146750436606</v>
+        <v>18.76080592907485</v>
       </c>
       <c r="L19" t="n">
-        <v>43.5820540957343</v>
+        <v>45.113140555002</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95121228325085</v>
+        <v>99.93740089470316</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.60235378824473</v>
+        <v>78.36938845177905</v>
       </c>
       <c r="C20" t="n">
-        <v>31.19614655602174</v>
+        <v>33.48248976741382</v>
       </c>
       <c r="D20" t="n">
-        <v>1.072610108309795</v>
+        <v>1.128987954055982</v>
       </c>
       <c r="E20" t="n">
-        <v>10.88793247725046</v>
+        <v>11.20502839729461</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7591961227224153</v>
+        <v>0.7517092502378809</v>
       </c>
       <c r="G20" t="n">
-        <v>18.49342900757862</v>
+        <v>20.41908355714865</v>
       </c>
       <c r="H20" t="n">
-        <v>37.42308007446918</v>
+        <v>38.59916800162705</v>
       </c>
       <c r="I20" t="n">
-        <v>1.221130230899157</v>
+        <v>1.567228477428118</v>
       </c>
       <c r="J20" t="n">
-        <v>4.744975767015093</v>
+        <v>4.698182813986755</v>
       </c>
       <c r="K20" t="n">
-        <v>25.39764621175527</v>
+        <v>21.63061154822095</v>
       </c>
       <c r="L20" t="n">
-        <v>43.36552508807804</v>
+        <v>44.83469253567964</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95931785585506</v>
+        <v>99.94779385131442</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.90978826371922</v>
+        <v>75.43129246232554</v>
       </c>
       <c r="C21" t="n">
-        <v>35.13888267526716</v>
+        <v>30.78438379114863</v>
       </c>
       <c r="D21" t="n">
-        <v>1.073373498797638</v>
+        <v>1.028306280619866</v>
       </c>
       <c r="E21" t="n">
-        <v>13.00389738748828</v>
+        <v>10.42357489722669</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597364524228378</v>
+        <v>0.7521433393355497</v>
       </c>
       <c r="G21" t="n">
-        <v>20.32688413386499</v>
+        <v>18.59813631392973</v>
       </c>
       <c r="H21" t="n">
-        <v>39.27000767826689</v>
+        <v>38.62145784042215</v>
       </c>
       <c r="I21" t="n">
-        <v>1.727536285235852</v>
+        <v>1.306777919944363</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748352827642734</v>
+        <v>4.700895870847186</v>
       </c>
       <c r="K21" t="n">
-        <v>19.09021173628078</v>
+        <v>24.56870753767447</v>
       </c>
       <c r="L21" t="n">
-        <v>45.71336200012696</v>
+        <v>44.6033745468039</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94245641167491</v>
+        <v>99.956465875627</v>
       </c>
     </row>
   </sheetData>
